--- a/artfynd/A 32060-2022 artfynd.xlsx
+++ b/artfynd/A 32060-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1298,10 +1298,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66700869</v>
+        <v>135255718</v>
       </c>
       <c r="B8" t="n">
-        <v>57141</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1309,21 +1309,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1331,22 +1331,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björksveden-Risten, Ög</t>
+          <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562254</v>
+        <v>562236</v>
       </c>
       <c r="R8" t="n">
-        <v>6464813</v>
+        <v>6464902</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1370,12 +1383,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129865365</v>
+        <v>66700869</v>
       </c>
       <c r="B9" t="n">
-        <v>4775</v>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,42 +1426,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Risten , Ög</t>
+          <t>Björksveden-Risten, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562240</v>
+        <v>562254</v>
       </c>
       <c r="R9" t="n">
-        <v>6464904</v>
+        <v>6464813</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1472,12 +1487,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2017-06-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2017-06-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,7 +1501,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1505,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122700373</v>
+        <v>129865365</v>
       </c>
       <c r="B10" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1530,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,13 +1559,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562246</v>
+        <v>562240</v>
       </c>
       <c r="R10" t="n">
-        <v>6464893</v>
+        <v>6464904</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1575,12 +1589,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,7 +1622,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129865364</v>
+        <v>122700373</v>
       </c>
       <c r="B11" t="n">
         <v>5179</v>
@@ -1648,13 +1662,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562240</v>
+        <v>562246</v>
       </c>
       <c r="R11" t="n">
-        <v>6464904</v>
+        <v>6464893</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1678,12 +1692,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1711,39 +1725,35 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>66700837</v>
+        <v>129865364</v>
       </c>
       <c r="B12" t="n">
-        <v>5495</v>
+        <v>5179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101410</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1751,17 +1761,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björksveden-Risten, Ög</t>
+          <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562322</v>
+        <v>562240</v>
       </c>
       <c r="R12" t="n">
-        <v>6464785</v>
+        <v>6464904</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,12 +1795,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1799,6 +1809,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1814,6 +1825,112 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>66700837</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Björksveden-Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>562322</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6464785</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2017-06-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2017-06-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32060-2022 artfynd.xlsx
+++ b/artfynd/A 32060-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67269771</v>
+        <v>135527456</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>92716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,43 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>757</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björksveden-Risten, Ög</t>
+          <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562250</v>
+        <v>562300</v>
       </c>
       <c r="R2" t="n">
-        <v>6464901</v>
+        <v>6464880</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-07-10</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-07-10</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68601946</v>
+        <v>67269771</v>
       </c>
       <c r="B3" t="n">
         <v>91909</v>
@@ -807,17 +804,23 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Byrumsskogen, Ög</t>
+          <t>Björksveden-Risten, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562256</v>
+        <v>562250</v>
       </c>
       <c r="R3" t="n">
-        <v>6464902</v>
+        <v>6464901</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -844,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-11-17</t>
+          <t>2017-07-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-12-07</t>
+          <t>2017-07-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -858,28 +861,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129865363</v>
+        <v>68601946</v>
       </c>
       <c r="B4" t="n">
-        <v>93235</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -887,44 +891,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Risten , Ög</t>
+          <t>Byrumsskogen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562240</v>
+        <v>562256</v>
       </c>
       <c r="R4" t="n">
-        <v>6464904</v>
+        <v>6464902</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -948,12 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2017-11-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2017-12-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -962,29 +959,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122700379</v>
+        <v>129865363</v>
       </c>
       <c r="B5" t="n">
-        <v>75428</v>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,24 +988,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1022,10 +1022,10 @@
         <v>562240</v>
       </c>
       <c r="R5" t="n">
-        <v>6464883</v>
+        <v>6464904</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,10 +1082,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66700859</v>
+        <v>122700379</v>
       </c>
       <c r="B6" t="n">
-        <v>79946</v>
+        <v>75428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,43 +1093,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björksveden-Risten, Ög</t>
+          <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562282</v>
+        <v>562240</v>
       </c>
       <c r="R6" t="n">
-        <v>6464806</v>
+        <v>6464883</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1150,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1167,6 +1164,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1185,32 +1183,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122700371</v>
+        <v>66700859</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1218,31 +1216,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Risten , Ög</t>
+          <t>Björksveden-Risten, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562246</v>
+        <v>562282</v>
       </c>
       <c r="R7" t="n">
-        <v>6464893</v>
+        <v>6464806</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1266,12 +1254,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2017-06-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2017-06-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1298,10 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135255718</v>
+        <v>122700371</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1336,11 +1324,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -1353,13 +1337,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562236</v>
+        <v>562246</v>
       </c>
       <c r="R8" t="n">
-        <v>6464902</v>
+        <v>6464893</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1383,12 +1367,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66700869</v>
+        <v>135255718</v>
       </c>
       <c r="B9" t="n">
-        <v>57141</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1426,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1448,22 +1432,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björksveden-Risten, Ög</t>
+          <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562254</v>
+        <v>562236</v>
       </c>
       <c r="R9" t="n">
-        <v>6464813</v>
+        <v>6464902</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1487,12 +1484,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129865365</v>
+        <v>66700869</v>
       </c>
       <c r="B10" t="n">
-        <v>4775</v>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1530,42 +1527,44 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Risten , Ög</t>
+          <t>Björksveden-Risten, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562240</v>
+        <v>562254</v>
       </c>
       <c r="R10" t="n">
-        <v>6464904</v>
+        <v>6464813</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1589,12 +1588,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2017-06-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2017-06-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,7 +1602,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1622,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122700373</v>
+        <v>129865365</v>
       </c>
       <c r="B11" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,21 +1631,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1662,13 +1660,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562246</v>
+        <v>562240</v>
       </c>
       <c r="R11" t="n">
-        <v>6464893</v>
+        <v>6464904</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1692,12 +1690,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,7 +1723,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129865364</v>
+        <v>122700373</v>
       </c>
       <c r="B12" t="n">
         <v>5179</v>
@@ -1765,13 +1763,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562240</v>
+        <v>562246</v>
       </c>
       <c r="R12" t="n">
-        <v>6464904</v>
+        <v>6464893</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1795,12 +1793,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1828,39 +1826,35 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>66700837</v>
+        <v>129865364</v>
       </c>
       <c r="B13" t="n">
-        <v>5495</v>
+        <v>5179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1868,17 +1862,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björksveden-Risten, Ög</t>
+          <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562322</v>
+        <v>562240</v>
       </c>
       <c r="R13" t="n">
-        <v>6464785</v>
+        <v>6464904</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1902,12 +1896,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1916,6 +1910,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1931,6 +1926,112 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>66700837</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Björksveden-Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>562322</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6464785</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2017-06-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2017-06-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32060-2022 artfynd.xlsx
+++ b/artfynd/A 32060-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135527456</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67269771</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,6 +989,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68601946</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129865363</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122700379</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66700859</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122700371</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1513,6 +1553,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255718</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66700869</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1720,6 +1770,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129865365</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1823,6 +1878,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122700373</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1926,6 +1986,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129865364</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2032,8 +2097,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66700837</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 32060-2022 artfynd.xlsx
+++ b/artfynd/A 32060-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135527456</v>
       </c>
       <c r="B2" t="n">
-        <v>92716</v>
+        <v>92758</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>135255718</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32060-2022 artfynd.xlsx
+++ b/artfynd/A 32060-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135527456</v>
       </c>
       <c r="B2" t="n">
-        <v>92758</v>
+        <v>92785</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32060-2022 artfynd.xlsx
+++ b/artfynd/A 32060-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67269771</v>
+        <v>135527456</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>92790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>757</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björksveden-Risten, Ög</t>
+          <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562250</v>
+        <v>562300</v>
       </c>
       <c r="R2" t="n">
-        <v>6464901</v>
+        <v>6464880</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-07-10</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-07-10</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,13 +780,13 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67269771</t>
+          <t>https://artportalen.se/Sighting/135527456</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68601946</v>
+        <v>67269771</v>
       </c>
       <c r="B3" t="n">
         <v>91909</v>
@@ -817,17 +814,23 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Byrumsskogen, Ög</t>
+          <t>Björksveden-Risten, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562256</v>
+        <v>562250</v>
       </c>
       <c r="R3" t="n">
-        <v>6464902</v>
+        <v>6464901</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -854,12 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-11-17</t>
+          <t>2017-07-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-12-07</t>
+          <t>2017-07-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,33 +871,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68601946</t>
+          <t>https://artportalen.se/Sighting/67269771</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129865363</v>
+        <v>68601946</v>
       </c>
       <c r="B4" t="n">
-        <v>93235</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,44 +906,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Risten , Ög</t>
+          <t>Byrumsskogen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562240</v>
+        <v>562256</v>
       </c>
       <c r="R4" t="n">
-        <v>6464904</v>
+        <v>6464902</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,12 +960,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2017-11-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2017-12-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,34 +974,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129865363</t>
+          <t>https://artportalen.se/Sighting/68601946</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122700379</v>
+        <v>129865363</v>
       </c>
       <c r="B5" t="n">
-        <v>75428</v>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,24 +1008,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1042,10 +1042,10 @@
         <v>562240</v>
       </c>
       <c r="R5" t="n">
-        <v>6464883</v>
+        <v>6464904</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,16 +1101,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122700379</t>
+          <t>https://artportalen.se/Sighting/129865363</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66700859</v>
+        <v>122700379</v>
       </c>
       <c r="B6" t="n">
-        <v>79946</v>
+        <v>75428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,43 +1118,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björksveden-Risten, Ög</t>
+          <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562282</v>
+        <v>562240</v>
       </c>
       <c r="R6" t="n">
-        <v>6464806</v>
+        <v>6464883</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,12 +1175,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,6 +1189,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1209,38 +1207,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66700859</t>
+          <t>https://artportalen.se/Sighting/122700379</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122700371</v>
+        <v>66700859</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1248,31 +1246,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Risten , Ög</t>
+          <t>Björksveden-Risten, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562246</v>
+        <v>562282</v>
       </c>
       <c r="R7" t="n">
-        <v>6464893</v>
+        <v>6464806</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,12 +1284,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2017-06-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2017-06-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,16 +1315,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122700371</t>
+          <t>https://artportalen.se/Sighting/66700859</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66700869</v>
+        <v>122700371</v>
       </c>
       <c r="B8" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1344,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1366,22 +1354,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björksveden-Risten, Ög</t>
+          <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562254</v>
+        <v>562246</v>
       </c>
       <c r="R8" t="n">
-        <v>6464813</v>
+        <v>6464893</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,12 +1402,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,16 +1433,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66700869</t>
+          <t>https://artportalen.se/Sighting/122700371</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129865365</v>
+        <v>135255718</v>
       </c>
       <c r="B9" t="n">
-        <v>4775</v>
+        <v>57977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,28 +1450,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1482,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562240</v>
+        <v>562236</v>
       </c>
       <c r="R9" t="n">
-        <v>6464904</v>
+        <v>6464902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,12 +1524,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1538,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1544,16 +1555,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129865365</t>
+          <t>https://artportalen.se/Sighting/135255718</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122700373</v>
+        <v>66700869</v>
       </c>
       <c r="B10" t="n">
-        <v>5179</v>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,42 +1572,44 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Risten , Ög</t>
+          <t>Björksveden-Risten, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562246</v>
+        <v>562254</v>
       </c>
       <c r="R10" t="n">
-        <v>6464893</v>
+        <v>6464813</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1620,12 +1633,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2017-06-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2017-06-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,7 +1647,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1652,16 +1664,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122700373</t>
+          <t>https://artportalen.se/Sighting/66700869</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129865364</v>
+        <v>129865365</v>
       </c>
       <c r="B11" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,21 +1681,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1760,45 +1772,41 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129865364</t>
+          <t>https://artportalen.se/Sighting/129865365</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>66700837</v>
+        <v>122700373</v>
       </c>
       <c r="B12" t="n">
-        <v>5495</v>
+        <v>5179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101410</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1806,17 +1814,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björksveden-Risten, Ög</t>
+          <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562322</v>
+        <v>562246</v>
       </c>
       <c r="R12" t="n">
-        <v>6464785</v>
+        <v>6464893</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1840,12 +1848,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1854,6 +1862,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1870,6 +1879,225 @@
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122700373</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129865364</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>562240</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6464904</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129865364</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>66700837</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Björksveden-Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>562322</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6464785</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2017-06-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2017-06-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/66700837</t>
         </is>
@@ -1888,6 +2116,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32060-2022 artfynd.xlsx
+++ b/artfynd/A 32060-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135527456</v>
       </c>
       <c r="B2" t="n">
-        <v>92790</v>
+        <v>92792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32060-2022 artfynd.xlsx
+++ b/artfynd/A 32060-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135527456</v>
       </c>
       <c r="B2" t="n">
-        <v>92792</v>
+        <v>92807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32060-2022 artfynd.xlsx
+++ b/artfynd/A 32060-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135527456</v>
       </c>
       <c r="B2" t="n">
-        <v>92807</v>
+        <v>92808</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
